--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.16486</v>
+        <v>17.33626</v>
       </c>
       <c r="D2" t="n">
-        <v>16.51306</v>
+        <v>16.96244</v>
       </c>
       <c r="E2" t="n">
-        <v>16.9108</v>
+        <v>17.20222</v>
       </c>
       <c r="F2" t="n">
-        <v>43.77501</v>
+        <v>43.03199</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05236</v>
+        <v>0.0514</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81365</v>
+        <v>1.8626</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.53085</v>
+        <v>17.34257</v>
       </c>
       <c r="D3" t="n">
-        <v>16.89542</v>
+        <v>16.59486</v>
       </c>
       <c r="E3" t="n">
-        <v>16.85728</v>
+        <v>16.94327</v>
       </c>
       <c r="F3" t="n">
-        <v>43.17459</v>
+        <v>42.35536</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05106</v>
+        <v>0.05194</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82448</v>
+        <v>1.86935</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.65513</v>
+        <v>16.88291</v>
       </c>
       <c r="D4" t="n">
-        <v>17.05502</v>
+        <v>16.72438</v>
       </c>
       <c r="E4" t="n">
-        <v>17.14668</v>
+        <v>16.73797</v>
       </c>
       <c r="F4" t="n">
-        <v>43.10696</v>
+        <v>42.98479</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05063</v>
+        <v>0.05108</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82392</v>
+        <v>1.85123</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.89664</v>
+        <v>16.64922</v>
       </c>
       <c r="D6" t="n">
-        <v>15.8025</v>
+        <v>15.73561</v>
       </c>
       <c r="E6" t="n">
-        <v>16.56845</v>
+        <v>16.52888</v>
       </c>
       <c r="F6" t="n">
-        <v>21.95053</v>
+        <v>21.67631</v>
       </c>
       <c r="G6" t="n">
-        <v>34.21352</v>
+        <v>34.86592</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.1226</v>
+        <v>17.15981</v>
       </c>
       <c r="D7" t="n">
-        <v>16.24603</v>
+        <v>16.05492</v>
       </c>
       <c r="E7" t="n">
-        <v>16.60619</v>
+        <v>16.67684</v>
       </c>
       <c r="F7" t="n">
-        <v>21.50552</v>
+        <v>22.04365</v>
       </c>
       <c r="G7" t="n">
-        <v>35.25714</v>
+        <v>34.23946</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.90361</v>
+        <v>16.76689</v>
       </c>
       <c r="D8" t="n">
-        <v>16.38005</v>
+        <v>16.28307</v>
       </c>
       <c r="E8" t="n">
-        <v>16.68875</v>
+        <v>16.60827</v>
       </c>
       <c r="F8" t="n">
-        <v>21.49155</v>
+        <v>22.21107</v>
       </c>
       <c r="G8" t="n">
-        <v>35.11124</v>
+        <v>35.27845</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.626</v>
+        <v>0.61726</v>
       </c>
       <c r="D10" t="n">
-        <v>1.14057</v>
+        <v>1.12856</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6166199999999999</v>
+        <v>0.62037</v>
       </c>
       <c r="D11" t="n">
-        <v>1.12749</v>
+        <v>1.13743</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61336</v>
+        <v>0.60414</v>
       </c>
       <c r="D12" t="n">
-        <v>1.11385</v>
+        <v>1.12739</v>
       </c>
     </row>
   </sheetData>
